--- a/artfynd/A 26946-2024 artfynd.xlsx
+++ b/artfynd/A 26946-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118304194</v>
+        <v>118304632</v>
       </c>
       <c r="B2" t="n">
-        <v>57290</v>
+        <v>57443</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Isaksflon (Isaksflon), Ång</t>
+          <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565939</v>
+        <v>565871</v>
       </c>
       <c r="R2" t="n">
-        <v>7061134</v>
+        <v>7061260</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118303928</v>
+        <v>118304194</v>
       </c>
       <c r="B5" t="n">
-        <v>78220</v>
+        <v>57290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Isaksflon (Isaksflon), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566019</v>
+        <v>565939</v>
       </c>
       <c r="R5" t="n">
-        <v>7061043</v>
+        <v>7061134</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118303861</v>
+        <v>118304638</v>
       </c>
       <c r="B6" t="n">
-        <v>56505</v>
+        <v>97846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,51 +1145,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Isaksflon (Isaksflon), Ång</t>
+          <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566032</v>
+        <v>565871</v>
       </c>
       <c r="R6" t="n">
-        <v>7061048</v>
+        <v>7061255</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118304161</v>
+        <v>118304423</v>
       </c>
       <c r="B7" t="n">
-        <v>56494</v>
+        <v>79565</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,39 +1265,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Isaksflon (Isaksflon), Ång</t>
+          <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565947</v>
+        <v>565902</v>
       </c>
       <c r="R7" t="n">
-        <v>7061115</v>
+        <v>7061229</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1330,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118304423</v>
+        <v>118304503</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
+        <v>79566</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565902</v>
+        <v>565904</v>
       </c>
       <c r="R8" t="n">
-        <v>7061229</v>
+        <v>7061207</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1442,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118304503</v>
+        <v>118303928</v>
       </c>
       <c r="B9" t="n">
-        <v>79566</v>
+        <v>78220</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,37 +1489,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Isaksflon (Isaksflon), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565904</v>
+        <v>566019</v>
       </c>
       <c r="R9" t="n">
-        <v>7061207</v>
+        <v>7061043</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,22 +1573,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118304632</v>
+        <v>118304161</v>
       </c>
       <c r="B10" t="n">
-        <v>57443</v>
+        <v>56494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,42 +1601,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Isaksflon (Isaksflon), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565871</v>
+        <v>565947</v>
       </c>
       <c r="R10" t="n">
-        <v>7061260</v>
+        <v>7061115</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1671,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,22 +1690,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118304638</v>
+        <v>118303861</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>56505</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,45 +1714,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Isaksflon (Isaksflon), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565871</v>
+        <v>566032</v>
       </c>
       <c r="R11" t="n">
-        <v>7061255</v>
+        <v>7061048</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 26946-2024 artfynd.xlsx
+++ b/artfynd/A 26946-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118304632</v>
+        <v>118304231</v>
       </c>
       <c r="B2" t="n">
-        <v>57443</v>
+        <v>79565</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Isaksflon (Isaksflon), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565871</v>
+        <v>565951</v>
       </c>
       <c r="R2" t="n">
-        <v>7061260</v>
+        <v>7061159</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118304231</v>
+        <v>118304638</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Isaksflon (Isaksflon), Ång</t>
+          <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565951</v>
+        <v>565871</v>
       </c>
       <c r="R3" t="n">
-        <v>7061159</v>
+        <v>7061255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118304672</v>
+        <v>118304503</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>79566</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565856</v>
+        <v>565904</v>
       </c>
       <c r="R4" t="n">
-        <v>7061249</v>
+        <v>7061207</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118304194</v>
+        <v>118304161</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>56494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1031,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1052,7 +1051,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565939</v>
+        <v>565947</v>
       </c>
       <c r="R5" t="n">
-        <v>7061134</v>
+        <v>7061115</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118304638</v>
+        <v>118304423</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,45 +1144,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565871</v>
+        <v>565902</v>
       </c>
       <c r="R6" t="n">
-        <v>7061255</v>
+        <v>7061229</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118304423</v>
+        <v>118303861</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>56505</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,41 +1256,51 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>102613</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Isaksflon (Isaksflon), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565902</v>
+        <v>566032</v>
       </c>
       <c r="R7" t="n">
-        <v>7061229</v>
+        <v>7061048</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118304503</v>
+        <v>118304672</v>
       </c>
       <c r="B8" t="n">
-        <v>79566</v>
+        <v>79565</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,13 +1406,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565904</v>
+        <v>565856</v>
       </c>
       <c r="R8" t="n">
-        <v>7061207</v>
+        <v>7061249</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,22 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118303928</v>
+        <v>118304632</v>
       </c>
       <c r="B9" t="n">
-        <v>78220</v>
+        <v>57443</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,34 +1494,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Isaksflon (Isaksflon), Ång</t>
+          <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566019</v>
+        <v>565871</v>
       </c>
       <c r="R9" t="n">
-        <v>7061043</v>
+        <v>7061260</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118304161</v>
+        <v>118304194</v>
       </c>
       <c r="B10" t="n">
-        <v>56494</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,16 +1611,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1621,7 +1631,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1630,13 +1640,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565947</v>
+        <v>565939</v>
       </c>
       <c r="R10" t="n">
-        <v>7061115</v>
+        <v>7061134</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,22 +1700,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118303861</v>
+        <v>118303928</v>
       </c>
       <c r="B11" t="n">
-        <v>56505</v>
+        <v>78220</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,51 +1724,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Isaksflon (Isaksflon), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566032</v>
+        <v>566019</v>
       </c>
       <c r="R11" t="n">
-        <v>7061048</v>
+        <v>7061043</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,12 +1812,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 26946-2024 artfynd.xlsx
+++ b/artfynd/A 26946-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118304231</v>
+        <v>118304632</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>57443</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Isaksflon (Isaksflon), Ång</t>
+          <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565951</v>
+        <v>565871</v>
       </c>
       <c r="R2" t="n">
-        <v>7061159</v>
+        <v>7061260</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118304638</v>
+        <v>118304231</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Isaksflon (Isaksflon), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565871</v>
+        <v>565951</v>
       </c>
       <c r="R3" t="n">
-        <v>7061255</v>
+        <v>7061159</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,12 +892,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -906,7 +907,7 @@
         <v>118304503</v>
       </c>
       <c r="B4" t="n">
-        <v>79566</v>
+        <v>79573</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1015,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118304161</v>
+        <v>118304638</v>
       </c>
       <c r="B5" t="n">
-        <v>56494</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,46 +1028,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Isaksflon (Isaksflon), Ång</t>
+          <t>Ottran (Ottran), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565947</v>
+        <v>565871</v>
       </c>
       <c r="R5" t="n">
-        <v>7061115</v>
+        <v>7061255</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118304423</v>
+        <v>118304672</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,13 +1172,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565902</v>
+        <v>565856</v>
       </c>
       <c r="R6" t="n">
-        <v>7061229</v>
+        <v>7061249</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,22 +1232,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118303861</v>
+        <v>118304161</v>
       </c>
       <c r="B7" t="n">
-        <v>56505</v>
+        <v>56494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,20 +1256,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1278,14 +1278,9 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1294,13 +1289,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566032</v>
+        <v>565947</v>
       </c>
       <c r="R7" t="n">
-        <v>7061048</v>
+        <v>7061115</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118304672</v>
+        <v>118304423</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,13 +1401,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565856</v>
+        <v>565902</v>
       </c>
       <c r="R8" t="n">
-        <v>7061249</v>
+        <v>7061229</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,22 +1461,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118304632</v>
+        <v>118303861</v>
       </c>
       <c r="B9" t="n">
-        <v>57443</v>
+        <v>56505</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,46 +1485,51 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Isaksflon (Isaksflon), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565871</v>
+        <v>566032</v>
       </c>
       <c r="R9" t="n">
-        <v>7061260</v>
+        <v>7061048</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,22 +1583,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118304194</v>
+        <v>118303928</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>78227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,39 +1611,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Isaksflon (Isaksflon), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565939</v>
+        <v>566019</v>
       </c>
       <c r="R10" t="n">
-        <v>7061134</v>
+        <v>7061043</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118303928</v>
+        <v>118304194</v>
       </c>
       <c r="B11" t="n">
-        <v>78220</v>
+        <v>57290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,34 +1723,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Isaksflon (Isaksflon), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566019</v>
+        <v>565939</v>
       </c>
       <c r="R11" t="n">
-        <v>7061043</v>
+        <v>7061134</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
